--- a/analysis_results.xlsx
+++ b/analysis_results.xlsx
@@ -14,54 +14,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
-  <si>
-    <t>Тема</t>
-  </si>
-  <si>
-    <t>Т-Банк разъяснения | Наличие</t>
-  </si>
-  <si>
-    <t>Т-Банк разъяснения | Совпадение</t>
-  </si>
-  <si>
-    <t>Т-Банк разъяснения | Балл</t>
-  </si>
-  <si>
-    <t>115-ФЗ | Наличие</t>
-  </si>
-  <si>
-    <t>115-ФЗ | Совпадение</t>
-  </si>
-  <si>
-    <t>115-ФЗ | Балл</t>
-  </si>
-  <si>
-    <t>Типы расхождений</t>
-  </si>
-  <si>
-    <t>Противоречия</t>
-  </si>
-  <si>
-    <t>Вывод</t>
-  </si>
-  <si>
-    <t>Положение ЦБ 860-П | Наличие</t>
-  </si>
-  <si>
-    <t>Положение ЦБ 860-П | Совпадение</t>
-  </si>
-  <si>
-    <t>Положение ЦБ 860-П | Балл</t>
-  </si>
-  <si>
-    <t>Блокирование (замораживание) средств</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+  <si>
+    <t>Понятие/требование</t>
+  </si>
+  <si>
+    <t>Документы сравнения</t>
+  </si>
+  <si>
+    <t>Как задано в 115-ФЗ</t>
+  </si>
+  <si>
+    <t>Как раскрыто в Положении ЦБ</t>
+  </si>
+  <si>
+    <t>Как раскрыто в материалах Т-Банка</t>
+  </si>
+  <si>
+    <t>Смысл совпадает?</t>
+  </si>
+  <si>
+    <t>Тип разрыва</t>
+  </si>
+  <si>
+    <t>Блокировка (замораживание) средств</t>
   </si>
   <si>
     <t>Операции, подлежащие обязательному контролю</t>
   </si>
   <si>
-    <t>Идентификация клиента</t>
+    <t>Упрощённая идентификация клиента</t>
   </si>
   <si>
     <t>Подозрительные операции</t>
@@ -70,88 +52,67 @@
     <t>Право отказа в проведении операции</t>
   </si>
   <si>
-    <t>Упрощенный контроль (до 15000 рублей)</t>
+    <t>Порядок проверки при блокировке счёта</t>
   </si>
   <si>
     <t>Внутренний контроль</t>
   </si>
   <si>
-    <t>явно</t>
-  </si>
-  <si>
-    <t>полное</t>
-  </si>
-  <si>
-    <t>частичное</t>
-  </si>
-  <si>
-    <t>0.630</t>
-  </si>
-  <si>
-    <t>0.407</t>
-  </si>
-  <si>
-    <t>неявно</t>
-  </si>
-  <si>
-    <t>отсутствует</t>
-  </si>
-  <si>
-    <t>отсутствие</t>
-  </si>
-  <si>
-    <t>0.382</t>
-  </si>
-  <si>
-    <t>0.601</t>
-  </si>
-  <si>
-    <t>0.456</t>
-  </si>
-  <si>
-    <t>0.348</t>
-  </si>
-  <si>
-    <t>0.188</t>
-  </si>
-  <si>
-    <t>0.156</t>
-  </si>
-  <si>
-    <t>0.160</t>
-  </si>
-  <si>
-    <t>терминологический</t>
+    <t>Оценка уровня риска клиента</t>
+  </si>
+  <si>
+    <t>115-ФЗ, №860-П, материалы Т-Банка</t>
+  </si>
+  <si>
+    <t>списание денежных средств с банковского счета (вклада, депозита), уменьшение остатка электронных денежных средств, выдача наличных денежных средств, совершение операций с иным имуществом такого клиента при проведении в отношении него процедур, примен...</t>
+  </si>
+  <si>
+    <t>Статья 6. Операции с денежными средствами или иным имуществом, подлежащие обязательному контролю</t>
+  </si>
+  <si>
+    <t>11-1. Идентификация клиента - физического лица, представителя клиента, выгодоприобретателя и бенефициарного владельца, упрощенная идентификация клиента - физического лица не проводятся при осуществлении операций по приему от клиентов - физических лиц...</t>
+  </si>
+  <si>
+    <t>При определении операции в качестве подлежащей обязательному контролю уполномоченный орган устанавливает вид данной операции, сумму ее совершения, организации, осуществляющие операции с денежными средствами или иным имуществом, представляющие сведени...</t>
+  </si>
+  <si>
+    <t>операторы связи, имеющие право самостоятельно оказывать услуги подвижной радиотелефонной связи, а также операторы связи, занимающие существенное положение в сети связи общего пользования, которые имеют право самостоятельно оказывать услуги связи по п...</t>
+  </si>
+  <si>
+    <t>Информация в документе не найдена или не относится к теме.</t>
+  </si>
+  <si>
+    <t>внутренний контроль - деятельность организаций, осуществляющих операции с денежными средствами или иным имуществом, по выявлению операций, подлежащих обязательному контролю, и иных операций с денежными средствами или иным имуществом, связанных с лега...</t>
+  </si>
+  <si>
+    <t>1. Требования в отношении идентификации клиента, представителя клиента и (или) выгодоприобретателя, бенефициарного владельца, установления иной информации о клиенте, обновления информации о них, оценки степени (уровня) риска совершения клиентом подоз...</t>
+  </si>
+  <si>
+    <t>6.1. Программа выявления в деятельности клиентов, в том числе являющихся пользователями платформы цифрового рубля, операций, подлежащих обязательному контролю, операций с цифровыми рублями, подлежащих обязательному контролю, подозрительных операций, ...</t>
+  </si>
+  <si>
+    <t>Создавайте сбор средств в приложении Т‑Банка, если ожидаете переводов от множества лиц. Например, когда вы покупаете подарок коллеге, собираете деньги на корпоратив или лечение кому‑нибудь. Так банку будет проще проверить эти операции: он уже будет з...</t>
+  </si>
+  <si>
+    <t>Не совершайте операции с криптовалютой. Прежде чем совершать операции с криптовалютами, рекомендуем изучить правовые стороны такой деятельности. Позиция Банка России по вопросу использования криптовалюты</t>
+  </si>
+  <si>
+    <t>Чтобы избежать неожиданной проверки, рекомендуем отслеживать статус бизнеса в сервисе Репутация. Узнать свою репутацию</t>
+  </si>
+  <si>
+    <t>Частично</t>
   </si>
   <si>
     <t>Нет</t>
   </si>
   <si>
-    <t>логический</t>
-  </si>
-  <si>
-    <t>По теме Блокирование (замораживание) средств: выявлены расхождения между документами (требуется ручная проверка).</t>
-  </si>
-  <si>
-    <t>По теме Операции, подлежащие обязательному контролю: выявлены расхождения между документами (требуется ручная проверка).</t>
-  </si>
-  <si>
-    <t>По теме Идентификация клиента: нормы в документах согласованы.</t>
-  </si>
-  <si>
-    <t>По теме Подозрительные операции: нормы в документах согласованы.</t>
-  </si>
-  <si>
-    <t>По теме Право отказа в проведении операции: выявлены расхождения между документами (требуется ручная проверка).</t>
-  </si>
-  <si>
-    <t>По теме Упрощенный контроль (до 15000 рублей): норма не обнаружена в представленных фрагментах.</t>
-  </si>
-  <si>
-    <t>По теме Внутренний контроль: норма не обнаружена в представленных фрагментах.</t>
-  </si>
-  <si>
-    <t>0.489</t>
+    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Т-Банк разъяснения, но отсутствует в Положение ЦБ 860-П</t>
+  </si>
+  <si>
+    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Положение ЦБ 860-П, но отсутствует в Т-Банк разъяснения</t>
+  </si>
+  <si>
+    <t>Тема не представлена в документах</t>
   </si>
 </sst>
 </file>
@@ -483,10 +444,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,211 +469,189 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/analysis_results.xlsx
+++ b/analysis_results.xlsx
@@ -106,10 +106,10 @@
     <t>Нет</t>
   </si>
   <si>
-    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Т-Банк разъяснения, но отсутствует в Положение ЦБ 860-П</t>
-  </si>
-  <si>
-    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Положение ЦБ 860-П, но отсутствует в Т-Банк разъяснения</t>
+    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Внутренние положения Т-Банка, но отсутствует в Положение ЦБ 860-П</t>
+  </si>
+  <si>
+    <t>Логический. Различие в содержании нормы: требование присутствует в 115-ФЗ, Положение ЦБ 860-П, но отсутствует в Внутренние положения Т-Банка</t>
   </si>
   <si>
     <t>Тема не представлена в документах</t>
